--- a/biblio/catalog.xlsx
+++ b/biblio/catalog.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр'!$A$1:$M$310</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр'!$A$1:$M$317</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Темы'!$A$1:$C$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Параметры'!$A$1:$G$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Параметры'!$A$1:$G$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Сводка'!$A$1:$B$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M310"/>
+  <dimension ref="A1:M317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -18741,7 +18741,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>2 / 2.3;2.5</t>
+          <t>2;3 / 2.3;2.4;2.5</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -18781,12 +18781,12 @@
       </c>
       <c r="L308" s="2" t="inlineStr">
         <is>
-          <t>εf(H, T, η); анизотропия; калибровка повреждения</t>
+          <t>εf(H, T, η); анизотропия; калибровка повреждения | деформация разрушения vs H, T и напряжённое состояние; калибровка GTN</t>
         </is>
       </c>
       <c r="M308" s="2" t="inlineStr">
         <is>
-          <t>СВР Zry-4, H до 1200 wt ppm; T = 25, 350, 480 °C; одноосное растяжение, EDC, плоская деформация</t>
+          <t>СВР Zry-4, H до 1200 wt ppm; T = 25, 350, 480 °C; одноосное растяжение, EDC, плоская деформация | CWSR Zry-4, H 0–1200 wt ppm, 20/350/480 °C: при 20 °C пластичность снижается с ростом H (растрескивание гидридов), при 350–480 °C слабо зависит от H</t>
         </is>
       </c>
     </row>
@@ -18908,8 +18908,429 @@
       </c>
       <c r="M310" s="2" t="inlineStr"/>
     </row>
+    <row r="311">
+      <c r="A311" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>Determination of fracture strength of δ-zirconium hydrides embedded in zirconium matrix at high temperatures</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>2 / 2.1;2.4</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>Определена прочность δ-гидридов, встроенных в матрицу Zr, при температурах до 250 °C (комбинация испытаний и расчёта напряжений в гидриде). Прочность гидрида почти не зависит от температуры. Оригинал числа, на которое опирается критерий разрушения хрупкого гидрида в мезомодели.</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>Kubo T.; Kobayashi Y.; Uchikoshi H.</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Nuclear Materials 435, 222–230</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>эксперимент</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2012.12.045</t>
+        </is>
+      </c>
+      <c r="J311" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="K311" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L311" s="2" t="inlineStr">
+        <is>
+          <t>прочность (критическое напряжение) гидрида для критерия хрупкого разрушения / CZM гидрида</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="inlineStr">
+        <is>
+          <t>σ_f гидрида ≈ 710 МПа, практически не зависит от T в 25–250 °C; в другой цитате 600–800 МПа (плоская деформация)</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>Determining failure properties of as-received and hydrided unirradiated Zircaloy-4 from ring compression tests</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>2;3 / 2.5;3.2</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>Сжатие колец Zry-4 (H до 610 wppm, 20 °C) и МКЭ с моделью вязкого повреждения для определения пластической деформации при разрушении и энергии разрушения. С ростом H обе величины падают, при 610 wppm разрушение хрупкое. Пример калибровки континуального повреждения гидрированной оболочки по RCT — прямой бенчмарк для CalculiX-модели.</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>Garrison B.E.; Yan Y.; TerMaath S.C.</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>Engineering Failure Analysis</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>модель</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.engfailanal.2021.105362</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="inlineStr">
+        <is>
+          <t>OA</t>
+        </is>
+      </c>
+      <c r="K312" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L312" s="2" t="inlineStr">
+        <is>
+          <t>калибровка вязкого повреждения по RCT; εf и энергия разрушения vs H</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="inlineStr">
+        <is>
+          <t>H до 610 wppm → хрупкое разрушение (Zry-4, RCT, 20 °C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>A microstructure-based modeling approach to predict the mechanical properties of Zr alloy with hydride precipitates</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>3 / 3.1</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>МКЭ по SEM-изображениям: матрица — кристаллическая пластичность ГПУ, гидриды — хрупкие с моделью повреждения, учтены остаточные напряжения от образования гидридов. Параметрическое исследование влияния доли, ориентации и толщины ламелей гидридов на свойства. Близкий аналог нашей мезомодели (явные хрупкие гидриды в пластичной матрице).</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>Kulkarni S.S.; Gupta V.; Senor D.; Truster T.; Soulami A.; Devanathan R.</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>Computational Materials Science</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>модель</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.commatsci.2021.110654</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="K313" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L313" s="2" t="inlineStr">
+        <is>
+          <t>постановка явных хрупких гидридов с повреждением; генерация геометрии по SEM</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>Sensitivity analysis of a twinning crystal plasticity finite element model (Zircaloy with hydride phase)</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>3 / 3.1</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>CPFE-модель Zircaloy с двойникованием и гидридной фазой; анализ чувствительности параметров. Доля гидридной фазы существенно влияет на механические свойства. Фон для калибровки матрицы и гидридов.</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>Kulkarni S.S.; Venkatraman A.; Senor D.; Devanathan R.</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>Computational Materials Science</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>модель</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.commatsci.2023.112425</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="K314" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L314" s="2" t="inlineStr">
+        <is>
+          <t>чувствительность CPFE к доле гидридов</t>
+        </is>
+      </c>
+      <c r="M314" s="2" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>Modeling and simulation of hydrogen behavior in Zircaloy-4 fuel cladding</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>3 / 3.5</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>Первая модель переноса водорода и выделения гидридов в BISON: диффузия, термодиффузия (эффект Соре), выделение/растворение. Водород накапливается в холодных зонах до выделения. База для последующей HNGD; модуля разрушения нет.</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>Courty O.; Motta A.T.; Hales J.D.</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>Journal of Nuclear Materials</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>модель</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnucmat.2014.05.013</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="inlineStr">
+        <is>
+          <t>OA</t>
+        </is>
+      </c>
+      <c r="K315" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L315" s="2" t="inlineStr">
+        <is>
+          <t>поля H/гидридов в оболочке из BISON</t>
+        </is>
+      </c>
+      <c r="M315" s="2" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>TRANSURANUS large-strain mechanical model for cladding ballooning under LOCA (Nucl. Eng. Des.)</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>3 / 3.5</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>Расширение TRANSURANUS на большие деформации ползучести при раздутии оболочки в LOCA; оценено влияние разных критериев разрушения на время до разрыва и деформацию. Пример критериев отказа оболочки в топливном коде (не гидридных).</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>? (JRC TRANSURANUS team)</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>Nuclear Engineering and Design</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>численный метод</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.nucengdes.2014.04.041</t>
+        </is>
+      </c>
+      <c r="J316" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="K316" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L316" s="2" t="inlineStr">
+        <is>
+          <t>критерии отказа оболочки в TRANSURANUS</t>
+        </is>
+      </c>
+      <c r="M316" s="2" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>The influence of multiaxial states of stress on the hydrogen embrittlement of zirconium alloy sheet</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>2;3 / 2.4;3.2</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>Охрупчивание листа Zircaloy-2 водородом при многоосном нагружении: зарождение пор на разрушенных гидридах, рост и слияние; слияние начинается при меньшей критической плотности пор при равнодвухосном растяжении, чем при одноосном. Классическая основа моделей повреждения с зарождением пор на гидридах.</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>Yunchang F.; Koss D.A.</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>Metallurgical Transactions A</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>эксперимент</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>10.1007/bf02814242</t>
+        </is>
+      </c>
+      <c r="J317" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="K317" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L317" s="2" t="inlineStr">
+        <is>
+          <t>механизм и критерий слияния пор от гидридов vs напряжённое состояние</t>
+        </is>
+      </c>
+      <c r="M317" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M310"/>
+  <autoFilter ref="A1:M317"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19077,7 +19498,7 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -19122,7 +19543,7 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -19137,7 +19558,7 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -19197,7 +19618,7 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -19212,7 +19633,7 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -19257,7 +19678,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -19272,7 +19693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -21010,8 +21431,108 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>CWSR Zry-4, H 0–1200 wt ppm, 20/350/480 °C</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>при 20 °C пластичность снижается с ростом H , при 350–480 °C слабо зависит от H</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>растрескивание гидридов</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Zry-4</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>σ_f гидрида ≈ 710 МПа, практически не зависит от T в 25–250 °C</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>в другой цитате 600–800 МПа</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>плоская деформация</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>H до 610 wppm → хрупкое разрушение</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Zry-4, RCT, 20 °C</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Zry-4</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>311</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G64"/>
+  <autoFilter ref="A1:G68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21048,7 +21569,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3">
@@ -21068,7 +21589,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
@@ -21078,7 +21599,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -21108,7 +21629,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9">
@@ -21128,7 +21649,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -21138,7 +21659,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -21148,7 +21669,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -21158,7 +21679,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -21168,7 +21689,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -21178,7 +21699,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16">
@@ -21188,7 +21709,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17">
@@ -21198,7 +21719,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18">
@@ -21208,7 +21729,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
@@ -21278,7 +21799,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
